--- a/stats for com eng/excel files/Ch4-06.xlsx
+++ b/stats for com eng/excel files/Ch4-06.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pin/Desktop/joint-repository/stats for com eng/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pin/Desktop/joint-repository/stats for com eng/excel files/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B16855A-23C7-C44C-B38F-C39A403317C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="24080" windowHeight="13180" activeTab="4" xr2:uid="{C748285C-19E1-4F2D-927D-6F526C53A5E8}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="20480" windowHeight="11080" activeTab="4" xr2:uid="{C748285C-19E1-4F2D-927D-6F526C53A5E8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="7" r:id="rId1"/>
@@ -1205,7 +1205,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1250,12 +1250,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1303,16 +1297,19 @@
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1376,8 +1373,8 @@
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>965200</xdr:colOff>
-          <xdr:row>16</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>254000</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1462,8 +1459,8 @@
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>939800</xdr:colOff>
-          <xdr:row>17</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>254000</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1853,7 +1850,7 @@
           <xdr:col>2</xdr:col>
           <xdr:colOff>965200</xdr:colOff>
           <xdr:row>17</xdr:row>
-          <xdr:rowOff>1233</xdr:rowOff>
+          <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1939,7 +1936,7 @@
           <xdr:col>2</xdr:col>
           <xdr:colOff>939800</xdr:colOff>
           <xdr:row>18</xdr:row>
-          <xdr:rowOff>1233</xdr:rowOff>
+          <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2103,8 +2100,8 @@
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>965200</xdr:colOff>
-          <xdr:row>17</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>254000</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2189,8 +2186,8 @@
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>939800</xdr:colOff>
-          <xdr:row>18</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>254000</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2773,7 +2770,7 @@
       <c r="B9" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="16">
         <v>0.05</v>
       </c>
     </row>
@@ -2796,13 +2793,13 @@
         <f>_xlfn.CHISQ.INV.RT(C9, C3-1)</f>
         <v>30.143527205646155</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="17" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="20" customHeight="1">
       <c r="A12" s="2"/>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="34" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="7" t="s">
@@ -2814,7 +2811,7 @@
     </row>
     <row r="13" spans="1:4" ht="20" customHeight="1">
       <c r="A13" s="2"/>
-      <c r="B13" s="17"/>
+      <c r="B13" s="35"/>
       <c r="C13" s="5" t="s">
         <v>8</v>
       </c>
@@ -2831,7 +2828,7 @@
         <f>_xlfn.CHISQ.DIST.RT(C10, C3-1)</f>
         <v>6.4892004939386794E-2</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="17" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3244,13 +3241,13 @@
         <f>_xlfn.NORM.S.INV(1-C10)</f>
         <v>1.6448536269514715</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="17" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="20" customHeight="1">
       <c r="A13" s="2"/>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="34" t="s">
         <v>3</v>
       </c>
       <c r="C13" s="12" t="s">
@@ -3262,7 +3259,7 @@
     </row>
     <row r="14" spans="1:4" ht="20" customHeight="1">
       <c r="A14" s="2"/>
-      <c r="B14" s="17"/>
+      <c r="B14" s="35"/>
       <c r="C14" s="14" t="s">
         <v>8</v>
       </c>
@@ -3276,7 +3273,7 @@
         <f>_xlfn.NORM.S.DIST(C11, TRUE)</f>
         <v>2.5787931810438501E-2</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="17" t="s">
         <v>40</v>
       </c>
     </row>
@@ -3469,7 +3466,7 @@
     </row>
     <row r="13" spans="1:4" ht="20" customHeight="1">
       <c r="A13" s="2"/>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="34" t="s">
         <v>3</v>
       </c>
       <c r="C13" s="12" t="s">
@@ -3479,7 +3476,7 @@
     </row>
     <row r="14" spans="1:4" ht="20" customHeight="1">
       <c r="A14" s="2"/>
-      <c r="B14" s="17"/>
+      <c r="B14" s="35"/>
       <c r="C14" s="14" t="s">
         <v>8</v>
       </c>
@@ -3574,179 +3571,179 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29F8094A-1FF1-4573-B68E-97EA7F90A965}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29F8094A-1FF1-4573-B68E-97EA7F90A965}">
   <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="22"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="20"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="22"/>
-      <c r="B2" s="22"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="22"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="20"/>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="22"/>
-      <c r="B3" s="23" t="s">
+      <c r="A3" s="20"/>
+      <c r="B3" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="24">
+      <c r="C3" s="22">
         <v>20</v>
       </c>
-      <c r="D3" s="22"/>
+      <c r="D3" s="20"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="22"/>
-      <c r="B4" s="25" t="s">
+      <c r="A4" s="20"/>
+      <c r="B4" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="24">
         <v>12</v>
       </c>
-      <c r="D4" s="22"/>
+      <c r="D4" s="20"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="22"/>
-      <c r="B5" s="25" t="s">
+      <c r="A5" s="20"/>
+      <c r="B5" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="25">
         <f>12/20</f>
         <v>0.6</v>
       </c>
-      <c r="D5" s="22"/>
+      <c r="D5" s="20"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="22"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="22"/>
-      <c r="B7" s="23" t="s">
+      <c r="A7" s="20"/>
+      <c r="B7" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="22"/>
+      <c r="D7" s="20"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="22"/>
-      <c r="B8" s="25" t="s">
+      <c r="A8" s="20"/>
+      <c r="B8" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="22"/>
+      <c r="D8" s="20"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="22"/>
-      <c r="B9" s="25" t="s">
+      <c r="A9" s="20"/>
+      <c r="B9" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="22"/>
+      <c r="D9" s="20"/>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="22"/>
-      <c r="B10" s="25" t="s">
+      <c r="A10" s="20"/>
+      <c r="B10" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="27">
         <v>0.05</v>
       </c>
-      <c r="D10" s="22" t="e" vm="1">
+      <c r="D10" s="20" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="22"/>
-      <c r="B11" s="25" t="s">
+      <c r="A11" s="20"/>
+      <c r="B11" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="25">
         <f>(C5-0.5)/SQRT(0.5*(1-0.5)/C3)</f>
         <v>0.89442719099991574</v>
       </c>
-      <c r="D11" s="22"/>
+      <c r="D11" s="20"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="22"/>
-      <c r="B12" s="30" t="s">
+      <c r="A12" s="20"/>
+      <c r="B12" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="29">
         <f>_xlfn.NORM.S.INV(1-C10/2)</f>
         <v>1.9599639845400536</v>
       </c>
-      <c r="D12" s="22"/>
+      <c r="D12" s="20"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="22"/>
-      <c r="B13" s="33" t="s">
+      <c r="A13" s="20"/>
+      <c r="B13" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="21"/>
+      <c r="D13" s="19"/>
     </row>
     <row r="14" spans="1:4" ht="18">
-      <c r="A14" s="22"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="36" t="s">
+      <c r="A14" s="20"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="22"/>
+      <c r="D14" s="20"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="22"/>
-      <c r="B15" s="25" t="s">
+      <c r="A15" s="20"/>
+      <c r="B15" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="29">
         <f>2*(1-_xlfn.NORM.S.DIST(C11, TRUE))</f>
         <v>0.37109336952269767</v>
       </c>
-      <c r="D15" s="22"/>
+      <c r="D15" s="20"/>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="22"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="22"/>
+      <c r="A16" s="20"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="20"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="22"/>
-      <c r="B17" s="22" t="s">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="22"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="20"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="22"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="22"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="20"/>
       <c r="E18" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="20" t="s">
         <v>53</v>
       </c>
     </row>
@@ -3755,6 +3752,5 @@
     <mergeCell ref="B13:B14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/stats for com eng/excel files/Ch4-06.xlsx
+++ b/stats for com eng/excel files/Ch4-06.xlsx
@@ -1,23 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pin/Desktop/joint-repository/stats for com eng/excel files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B16855A-23C7-C44C-B38F-C39A403317C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A5A453-DABF-6E47-ACDE-C6BFE34D29CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="20480" windowHeight="11080" activeTab="4" xr2:uid="{C748285C-19E1-4F2D-927D-6F526C53A5E8}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="20480" windowHeight="11000" firstSheet="2" activeTab="9" xr2:uid="{C748285C-19E1-4F2D-927D-6F526C53A5E8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="7" r:id="rId1"/>
-    <sheet name="Sheet4" sheetId="9" r:id="rId2"/>
-    <sheet name="Sheet5" sheetId="8" r:id="rId3"/>
-    <sheet name="Sheet6" sheetId="10" r:id="rId4"/>
-    <sheet name="Sheet7" sheetId="11" r:id="rId5"/>
+    <sheet name="Sheet3 practice" sheetId="13" r:id="rId2"/>
+    <sheet name="Sheet4" sheetId="9" r:id="rId3"/>
+    <sheet name="Sheet4 practice" sheetId="14" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="8" r:id="rId5"/>
+    <sheet name="Sheet5 practice" sheetId="15" r:id="rId6"/>
+    <sheet name="Sheet6" sheetId="10" r:id="rId7"/>
+    <sheet name="Sheet6 practice" sheetId="16" r:id="rId8"/>
+    <sheet name="Sheet7" sheetId="11" r:id="rId9"/>
+    <sheet name="Sheet7 practice" sheetId="12" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -62,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="93">
   <si>
     <t>Parameter of Interest</t>
   </si>
@@ -953,6 +958,117 @@
   </si>
   <si>
     <t>accept</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>s^2</t>
+  </si>
+  <si>
+    <t>sigma^2 &gt; 0.01</t>
+  </si>
+  <si>
+    <t>sigma^2 = 0.01</t>
+  </si>
+  <si>
+    <t>alpha</t>
+  </si>
+  <si>
+    <t>test statistics</t>
+  </si>
+  <si>
+    <t>critical value</t>
+  </si>
+  <si>
+    <t>P value</t>
+  </si>
+  <si>
+    <t>H0</t>
+  </si>
+  <si>
+    <t>H1</t>
+  </si>
+  <si>
+    <t>sigma^2 != 0.01</t>
+  </si>
+  <si>
+    <t>upper bound</t>
+  </si>
+  <si>
+    <t>lower bound</t>
+  </si>
+  <si>
+    <t>reject</t>
+  </si>
+  <si>
+    <t>Infer about population using sample, in variance, chi square test</t>
+  </si>
+  <si>
+    <t>sigma^2 hyp</t>
+  </si>
+  <si>
+    <t>s^2 sam var</t>
+  </si>
+  <si>
+    <t>We don’t have strong enough evidence to reject H0, thus, what we can say is that from sample, liquid detergent manufacturer has no problem with their product</t>
+  </si>
+  <si>
+    <t>Chi square two tail test</t>
+  </si>
+  <si>
+    <t>Test statistic</t>
+  </si>
+  <si>
+    <t>CI</t>
+  </si>
+  <si>
+    <t>We have strong enough evidence to reject null hypothesis</t>
+  </si>
+  <si>
+    <t>p0 = 0.05</t>
+  </si>
+  <si>
+    <t>defect</t>
+  </si>
+  <si>
+    <t>P_hat</t>
+  </si>
+  <si>
+    <t>test statistic</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>p0 &lt; 0.05</t>
+  </si>
+  <si>
+    <t>We have strong evidence to reject H0, meaning that the defective exceeds 0.5 step</t>
+  </si>
+  <si>
+    <t>defective, yes or no, percent, PROPORTION</t>
+  </si>
+  <si>
+    <t>P0 &gt; 0.6</t>
+  </si>
+  <si>
+    <t>aceept</t>
+  </si>
+  <si>
+    <t>We don't have strong enough evidence to reject H0, thus, we can proportion of voters of this year's pop is above 60%</t>
+  </si>
+  <si>
+    <t>P0 = 0.5</t>
+  </si>
+  <si>
+    <t>P0 != 0.5</t>
+  </si>
+  <si>
+    <t>2T</t>
+  </si>
+  <si>
+    <t>Since we don't have a strong enough evidence to reject H0, we can say that friend's coin is fair</t>
   </si>
 </sst>
 </file>
@@ -1205,7 +1321,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1298,18 +1414,19 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1331,16 +1448,44 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" checked="Checked" firstButton="1" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp10.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp11.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" firstButton="1" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" checked="Checked" firstButton="1" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" checked="Checked" firstButton="1" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" firstButton="1" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" checked="Checked" firstButton="1" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1352,11 +1497,15 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" checked="Checked" firstButton="1" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" firstButton="1" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Radio" firstButton="1" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1599,6 +1748,227 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>12700</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>25400</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>965200</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="13313" name="Option Button 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s13313"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000001340000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>Accept H0</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>12700</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>25400</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>939800</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="13314" name="Option Button 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s13314"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002340000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>Reject H0</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1270000</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>200526</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>420214</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>241077</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7730CE55-D2F5-9ACA-EE28-406F1C9FA5AC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6372281" y="712982"/>
+          <a:ext cx="5054600" cy="4140200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
@@ -1683,7 +2053,7 @@
                   <a14:compatExt spid="_x0000_s8193"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000001200000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000001200000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1769,7 +2139,7 @@
                   <a14:compatExt spid="_x0000_s8194"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002200000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002200000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1835,7 +2205,289 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>66676</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D02D5332-8B3E-7642-BF5F-8E9432B716B5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6378575" y="2155825"/>
+          <a:ext cx="1308100" cy="527050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>12700</xdr:colOff>
+          <xdr:row>14</xdr:row>
+          <xdr:rowOff>25400</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>965200</xdr:colOff>
+          <xdr:row>14</xdr:row>
+          <xdr:rowOff>251283</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="14337" name="Option Button 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s14337"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000001380000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>Accept H0</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>12700</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>25400</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>939800</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="14338" name="Option Button 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s14338"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002380000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>Reject H0</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>354418</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>147675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>589585</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>244169</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62C51D1C-A947-2468-F560-96520148D5ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8646230" y="663037"/>
+          <a:ext cx="4007756" cy="1127219"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -1849,8 +2501,8 @@
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>965200</xdr:colOff>
-          <xdr:row>17</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>254000</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1860,7 +2512,7 @@
                   <a14:compatExt spid="_x0000_s7169"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-0000011C0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-0000011C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1935,8 +2587,8 @@
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>939800</xdr:colOff>
-          <xdr:row>18</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>254000</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1946,7 +2598,7 @@
                   <a14:compatExt spid="_x0000_s7170"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-0000021C0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-0000021C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2086,7 +2738,346 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>12700</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>25400</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>965200</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>2170</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="22529" name="Option Button 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s22529"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A89188D3-A415-FC4D-B063-BE14638E7765}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>Accept H0</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>12700</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>25400</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>939800</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="22530" name="Option Button 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s22530"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9665E2E-20B5-934D-9102-7FA08F9ED784}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>Reject H0</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>139700</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>46839</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1339850</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>234950</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCC950EF-8FFB-0D4B-A2E6-2C4C7D8F5126}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5245100" y="2332839"/>
+          <a:ext cx="1200150" cy="442111"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1473200</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>132080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>528320</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>196941</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0B1A24D-4C0B-9133-258B-68F8749A7ABA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6583680" y="386080"/>
+          <a:ext cx="4318000" cy="1842861"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>312615</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>33643</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>198315</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>238705</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18125092-DD2E-388F-209C-280EA3154149}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13319648" y="1824669"/>
+          <a:ext cx="1206872" cy="460922"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -2111,7 +3102,7 @@
                   <a14:compatExt spid="_x0000_s10241"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000001280000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000001280000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2197,7 +3188,7 @@
                   <a14:compatExt spid="_x0000_s10242"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002280000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002280000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2330,6 +3321,276 @@
             </a14:hiddenLine>
           </a:ext>
         </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>12700</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>25400</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>965200</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>1744</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="23553" name="Option Button 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s23553"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9364EF36-A8E6-634D-8812-AB46099631DC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>Accept H0</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>12700</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>25400</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>939800</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="23554" name="Option Button 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s23554"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{039AD1FB-178A-D048-94AE-23A9C9ED72D2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>Reject H0</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1337733</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>186266</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>376767</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>211666</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA907055-DA93-0FC7-AF36-EEEE26D4707B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6451600" y="186266"/>
+          <a:ext cx="7607300" cy="3581400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>81280</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>396240</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>186787</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46B4CECB-7342-233B-C44D-A533931BC820}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="81280"/>
+          <a:ext cx="7772400" cy="2848707"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -2799,7 +4060,7 @@
     </row>
     <row r="12" spans="1:4" ht="20" customHeight="1">
       <c r="A12" s="2"/>
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="32" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="7" t="s">
@@ -2811,7 +4072,7 @@
     </row>
     <row r="13" spans="1:4" ht="20" customHeight="1">
       <c r="A13" s="2"/>
-      <c r="B13" s="35"/>
+      <c r="B13" s="33"/>
       <c r="C13" s="5" t="s">
         <v>8</v>
       </c>
@@ -2919,7 +4180,496 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D65245E-A2E8-CA40-9C7B-51515C822F42}">
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="20"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="20"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="20"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="20"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="20"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="20"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="20"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="20"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="20"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="20"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="20"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="20"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="20"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="20"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="20"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="20"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="20"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="20"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="20"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="20"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="20"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="20"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="19"/>
+    </row>
+    <row r="14" spans="1:4" ht="18">
+      <c r="A14" s="20"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="20"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="20"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="20"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="30">
+        <v>20</v>
+      </c>
+      <c r="D16" s="20"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="19">
+        <v>12</v>
+      </c>
+      <c r="D17" s="20"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="20"/>
+      <c r="B18" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="19">
+        <f>C17/C16</f>
+        <v>0.6</v>
+      </c>
+      <c r="D18" s="20"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="B20" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="B21" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="B22" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="B23" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="D23" t="s">
+        <v>67</v>
+      </c>
+      <c r="E23">
+        <f>_xlfn.NORM.S.INV(1-C22)</f>
+        <v>1.6448536269514715</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="D24" t="s">
+        <v>68</v>
+      </c>
+      <c r="E24">
+        <f>_xlfn.NORM.S.INV(C22)</f>
+        <v>-1.6448536269514726</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="B25" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25">
+        <f>(C18-D20)/SQRT(D20*(1-D20)/C16)</f>
+        <v>0.89442719099991574</v>
+      </c>
+      <c r="D25" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="B27" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27">
+        <f>C22</f>
+        <v>0.05</v>
+      </c>
+      <c r="F27" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="B28" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28">
+        <f>2*(1-_xlfn.NORM.S.DIST(ABS(C25), TRUE))</f>
+        <v>0.37109336952269767</v>
+      </c>
+      <c r="D28" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B13:B14"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{821FDB35-715A-DC42-A02D-E86CDDAFEEE1}">
+  <dimension ref="A1:N24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="20" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="5.6640625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="32.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="8.6640625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="20" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="20" customHeight="1">
+      <c r="A2" s="2"/>
+    </row>
+    <row r="3" spans="1:13" ht="20" customHeight="1">
+      <c r="A3" s="2"/>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6"/>
+    </row>
+    <row r="4" spans="1:13" ht="20" customHeight="1">
+      <c r="A4" s="2"/>
+      <c r="B4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="9"/>
+    </row>
+    <row r="5" spans="1:13" ht="20" customHeight="1">
+      <c r="A5" s="2"/>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="1:13" ht="20" customHeight="1">
+      <c r="A6" s="2"/>
+      <c r="B6" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="7"/>
+    </row>
+    <row r="7" spans="1:13" ht="20" customHeight="1">
+      <c r="A7" s="2"/>
+      <c r="B7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="7"/>
+    </row>
+    <row r="8" spans="1:13" ht="20" customHeight="1">
+      <c r="A8" s="2"/>
+      <c r="B8" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="7"/>
+    </row>
+    <row r="9" spans="1:13" ht="20" customHeight="1">
+      <c r="A9" s="2"/>
+      <c r="B9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="16"/>
+    </row>
+    <row r="10" spans="1:13" ht="20" customHeight="1">
+      <c r="A10" s="2"/>
+      <c r="B10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="9"/>
+    </row>
+    <row r="11" spans="1:13" ht="20" customHeight="1">
+      <c r="A11" s="2"/>
+      <c r="B11" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="8"/>
+      <c r="D11" s="17"/>
+      <c r="L11" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="20" customHeight="1">
+      <c r="A12" s="2"/>
+      <c r="B12" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" ht="20" customHeight="1">
+      <c r="A13" s="2"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="5"/>
+      <c r="L13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M13" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="20" customHeight="1">
+      <c r="A14" s="2"/>
+      <c r="B14" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="8"/>
+      <c r="D14" s="17"/>
+      <c r="L14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M14" s="2">
+        <v>1.5299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="20" customHeight="1">
+      <c r="A15" s="2"/>
+      <c r="C15" s="4"/>
+      <c r="L15" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M15" s="2">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="20" customHeight="1">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="20" customHeight="1">
+      <c r="A17" s="2"/>
+      <c r="L17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="20" customHeight="1">
+      <c r="A18" s="2"/>
+      <c r="L18" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="20" customHeight="1">
+      <c r="B19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M19" s="2">
+        <f>(M13-1)*M14/0.01</f>
+        <v>29.07</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="20" customHeight="1">
+      <c r="B20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="M20" s="2">
+        <f>_xlfn.CHISQ.INV(1-M15, M13-1)</f>
+        <v>30.143527205646159</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="20" customHeight="1">
+      <c r="L21" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M21" s="2">
+        <f>M15</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="20" customHeight="1">
+      <c r="L22" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="M22" s="2">
+        <f>1-_xlfn.CHISQ.DIST(M19,M13-1,TRUE)</f>
+        <v>6.4892004939386849E-2</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="20" customHeight="1">
+      <c r="L24" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B12:B13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="13313" r:id="rId4" name="Option Button 1">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>12700</xdr:colOff>
+                    <xdr:row>15</xdr:row>
+                    <xdr:rowOff>25400</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>965200</xdr:colOff>
+                    <xdr:row>16</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="13314" r:id="rId5" name="Option Button 2">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>12700</xdr:colOff>
+                    <xdr:row>16</xdr:row>
+                    <xdr:rowOff>25400</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>939800</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{160F5C47-B0A6-42EC-B202-BF4B54B4F253}">
   <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="20" customHeight="1"/>
@@ -3134,7 +4884,319 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26367F19-A8FE-514E-B48D-148F71CF5173}">
+  <dimension ref="A1:N21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="20" customHeight="1"/>
+  <cols>
+    <col min="2" max="2" width="29.6640625" customWidth="1"/>
+    <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="20" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2" spans="1:14" ht="20" customHeight="1">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:14" ht="20" customHeight="1">
+      <c r="A3" s="2"/>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6">
+        <v>101</v>
+      </c>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:14" ht="20" customHeight="1">
+      <c r="A4" s="2"/>
+      <c r="B4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="15">
+        <v>3.9690000000000001E-5</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4">
+        <v>6.3E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="20" customHeight="1">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:14" ht="20" customHeight="1">
+      <c r="A6" s="2"/>
+      <c r="B6" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:14" ht="20" customHeight="1">
+      <c r="A7" s="2"/>
+      <c r="B7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" ht="20" customHeight="1">
+      <c r="A8" s="2"/>
+      <c r="B8" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:14" ht="20" customHeight="1">
+      <c r="A9" s="2"/>
+      <c r="B9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="7">
+        <f>1-0.95</f>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="J9" t="s">
+        <v>76</v>
+      </c>
+      <c r="K9" s="36">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="20" customHeight="1">
+      <c r="A10" s="2"/>
+      <c r="B10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="9">
+        <f>(C3-1)*C4/0.01</f>
+        <v>0.39690000000000003</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="J10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K10">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="20" customHeight="1">
+      <c r="A11" s="2"/>
+      <c r="B11" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="8">
+        <f>_xlfn.CHISQ.INV.RT(C9/2, C3-1)</f>
+        <v>129.56119718583659</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="J11" t="s">
+        <v>57</v>
+      </c>
+      <c r="K11">
+        <v>3.9690000000000001E-5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="20" customHeight="1">
+      <c r="A12" s="2"/>
+      <c r="B12" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="8">
+        <f>_xlfn.CHISQ.INV.RT(1-C9/2, C3-1)</f>
+        <v>74.221927474923731</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="J12" t="s">
+        <v>60</v>
+      </c>
+      <c r="K12">
+        <f>1-0.95</f>
+        <v>5.0000000000000044E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="20" customHeight="1">
+      <c r="A13" s="2"/>
+      <c r="B13" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="J13" t="s">
+        <v>64</v>
+      </c>
+      <c r="K13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="20" customHeight="1">
+      <c r="J14" t="s">
+        <v>65</v>
+      </c>
+      <c r="K14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="20" customHeight="1">
+      <c r="B15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="J15" t="s">
+        <v>74</v>
+      </c>
+      <c r="M15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N15">
+        <f>_xlfn.CHISQ.INV.RT(K12, K10-1)</f>
+        <v>124.34211340400408</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="20" customHeight="1">
+      <c r="B16" s="2"/>
+      <c r="C16" s="3"/>
+      <c r="J16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N16">
+        <f>_xlfn.CHISQ.INV(K12, K10-1)</f>
+        <v>77.929465165017263</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="20" customHeight="1">
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="J17" t="s">
+        <v>75</v>
+      </c>
+      <c r="K17">
+        <f>(K10-1)*K11/0.01</f>
+        <v>0.39690000000000003</v>
+      </c>
+      <c r="L17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="20" customHeight="1">
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="J18" t="s">
+        <v>60</v>
+      </c>
+      <c r="K18">
+        <f>K12</f>
+        <v>5.0000000000000044E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="20" customHeight="1">
+      <c r="J19" t="s">
+        <v>63</v>
+      </c>
+      <c r="K19">
+        <f>2*_xlfn.CHISQ.DIST(K17, K10-1, TRUE)</f>
+        <v>4.1306427068686812E-100</v>
+      </c>
+      <c r="L19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="20" customHeight="1">
+      <c r="J21" t="s">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="14337" r:id="rId3" name="Option Button 1">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>12700</xdr:colOff>
+                    <xdr:row>14</xdr:row>
+                    <xdr:rowOff>25400</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>965200</xdr:colOff>
+                    <xdr:row>15</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="14338" r:id="rId4" name="Option Button 2">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>12700</xdr:colOff>
+                    <xdr:row>15</xdr:row>
+                    <xdr:rowOff>25400</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>939800</xdr:colOff>
+                    <xdr:row>16</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7EF0F67-C83F-4E13-8CD1-9D5DF9EDC28E}">
   <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="20" customHeight="1"/>
@@ -3247,7 +5309,7 @@
     </row>
     <row r="13" spans="1:4" ht="20" customHeight="1">
       <c r="A13" s="2"/>
-      <c r="B13" s="34" t="s">
+      <c r="B13" s="32" t="s">
         <v>3</v>
       </c>
       <c r="C13" s="12" t="s">
@@ -3259,7 +5321,7 @@
     </row>
     <row r="14" spans="1:4" ht="20" customHeight="1">
       <c r="A14" s="2"/>
-      <c r="B14" s="35"/>
+      <c r="B14" s="33"/>
       <c r="C14" s="14" t="s">
         <v>8</v>
       </c>
@@ -3356,7 +5418,310 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F986375-8EFE-904A-A65E-DE3866F00A31}">
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="20" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="5.6640625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="32.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="8.6640625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="20" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="20" customHeight="1">
+      <c r="A2" s="2"/>
+      <c r="L2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M2" s="2">
+        <f>200</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="20" customHeight="1">
+      <c r="A3" s="2"/>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6">
+        <v>200</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="M3" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="20" customHeight="1">
+      <c r="A4" s="2"/>
+      <c r="B4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="6">
+        <v>4</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="M4" s="2">
+        <f>M3/M2</f>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="20" customHeight="1">
+      <c r="A5" s="2"/>
+      <c r="B5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="9">
+        <f>C4/C3</f>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="20" customHeight="1">
+      <c r="A6" s="2"/>
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:14" ht="20" customHeight="1">
+      <c r="A7" s="2"/>
+      <c r="B7" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="20" customHeight="1">
+      <c r="A8" s="2"/>
+      <c r="B8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="20" customHeight="1">
+      <c r="A9" s="2"/>
+      <c r="B9" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" s="2">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="20" customHeight="1">
+      <c r="A10" s="2"/>
+      <c r="B10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="20" customHeight="1">
+      <c r="A11" s="2"/>
+      <c r="B11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="9">
+        <f>(C5-0.05)/SQRT(0.05*(1-0.05)/C3)</f>
+        <v>-1.9466570535691505</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="M11" s="2">
+        <f>_xlfn.NORM.S.INV(M9)</f>
+        <v>-1.6448536269514726</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="20" customHeight="1">
+      <c r="A12" s="2"/>
+      <c r="B12" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="8">
+        <f>_xlfn.NORM.S.INV(1-C10)</f>
+        <v>1.6448536269514715</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="M12" s="2">
+        <f>(M4-N7)/(SQRT(N7*(1-N7)/M2))</f>
+        <v>-1.9466570535691505</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="20" customHeight="1">
+      <c r="A13" s="2"/>
+      <c r="B13" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M13" s="2">
+        <f>M9</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="20" customHeight="1">
+      <c r="A14" s="2"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="M14" s="2">
+        <f>_xlfn.NORM.S.DIST(M12, TRUE)</f>
+        <v>2.5787931810438501E-2</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="20" customHeight="1">
+      <c r="A15" s="2"/>
+      <c r="B15" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="8">
+        <f>_xlfn.NORM.S.DIST(C11, TRUE)</f>
+        <v>2.5787931810438501E-2</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="20" customHeight="1">
+      <c r="A16" s="2"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="20" customHeight="1">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="20" customHeight="1">
+      <c r="A18" s="2"/>
+    </row>
+    <row r="19" spans="1:2" ht="20" customHeight="1">
+      <c r="A19" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B13:B14"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="22529" r:id="rId3" name="Option Button 1">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>12700</xdr:colOff>
+                    <xdr:row>16</xdr:row>
+                    <xdr:rowOff>25400</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>965200</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="22530" r:id="rId4" name="Option Button 2">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>12700</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>25400</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>939800</xdr:colOff>
+                    <xdr:row>18</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2CF0754-77DE-4E76-80D9-837B5A5943EF}">
   <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="20" customHeight="1"/>
@@ -3466,7 +5831,7 @@
     </row>
     <row r="13" spans="1:4" ht="20" customHeight="1">
       <c r="A13" s="2"/>
-      <c r="B13" s="34" t="s">
+      <c r="B13" s="32" t="s">
         <v>3</v>
       </c>
       <c r="C13" s="12" t="s">
@@ -3476,7 +5841,7 @@
     </row>
     <row r="14" spans="1:4" ht="20" customHeight="1">
       <c r="A14" s="2"/>
-      <c r="B14" s="35"/>
+      <c r="B14" s="33"/>
       <c r="C14" s="14" t="s">
         <v>8</v>
       </c>
@@ -3570,7 +5935,304 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{037E749B-61E9-E745-9D86-E08CFDFA710F}">
+  <dimension ref="A1:R19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="20" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="5.6640625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="32.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="8.6640625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="20" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="20" customHeight="1">
+      <c r="A2" s="2"/>
+    </row>
+    <row r="3" spans="1:18" ht="20" customHeight="1">
+      <c r="A3" s="2"/>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="20" customHeight="1">
+      <c r="A4" s="2"/>
+      <c r="B4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="6">
+        <v>92</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="20" customHeight="1">
+      <c r="A5" s="2"/>
+      <c r="B5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="9">
+        <f>C4/C3</f>
+        <v>0.6216216216216216</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="20" customHeight="1">
+      <c r="A6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="P6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="20" customHeight="1">
+      <c r="A7" s="2"/>
+      <c r="B7" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q7" s="2">
+        <f>Q6/Q5</f>
+        <v>0.6216216216216216</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="20" customHeight="1">
+      <c r="A8" s="2"/>
+      <c r="B8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="20" customHeight="1">
+      <c r="A9" s="2"/>
+      <c r="B9" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="20" customHeight="1">
+      <c r="A10" s="2"/>
+      <c r="B10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="R10" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="20" customHeight="1">
+      <c r="A11" s="2"/>
+      <c r="B11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="9">
+        <f>(C5-0.6)/SQRT(0.6*(1-0.6)/C3)</f>
+        <v>0.53692484417121955</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="20" customHeight="1">
+      <c r="A12" s="2"/>
+      <c r="B12" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="8">
+        <f>_xlfn.NORM.S.INV(1-C10)</f>
+        <v>1.6448536269514715</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="20" customHeight="1">
+      <c r="A13" s="2"/>
+      <c r="B13" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="P13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q13" s="2">
+        <f>_xlfn.NORM.S.INV(1-Q9)</f>
+        <v>1.6448536269514715</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="20" customHeight="1">
+      <c r="A14" s="2"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q14" s="2">
+        <f>(Q7-R10)/SQRT(R10*(1-R10)/Q5)</f>
+        <v>0.53692484417121955</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="20" customHeight="1">
+      <c r="A15" s="2"/>
+      <c r="B15" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="8">
+        <f>1-_xlfn.NORM.S.DIST(C11, TRUE)</f>
+        <v>0.29565976453295295</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q15" s="2">
+        <f>Q9</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="20" customHeight="1">
+      <c r="A16" s="2"/>
+      <c r="C16" s="4"/>
+      <c r="P16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q16" s="2">
+        <f>1-_xlfn.NORM.S.DIST(Q14, TRUE)</f>
+        <v>0.29565976453295295</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="20" customHeight="1">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="20" customHeight="1">
+      <c r="A18" s="2"/>
+      <c r="P18" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="20" customHeight="1">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B13:B14"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="23553" r:id="rId3" name="Option Button 1">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>12700</xdr:colOff>
+                    <xdr:row>16</xdr:row>
+                    <xdr:rowOff>25400</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>965200</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="23554" r:id="rId4" name="Option Button 2">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>12700</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>25400</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>939800</xdr:colOff>
+                    <xdr:row>18</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29F8094A-1FF1-4573-B68E-97EA7F90A965}">
   <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
@@ -3692,7 +6354,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="20"/>
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="34" t="s">
         <v>3</v>
       </c>
       <c r="C13" s="27" t="s">
@@ -3702,7 +6364,7 @@
     </row>
     <row r="14" spans="1:4" ht="18">
       <c r="A14" s="20"/>
-      <c r="B14" s="33"/>
+      <c r="B14" s="35"/>
       <c r="C14" s="31" t="s">
         <v>54</v>
       </c>
